--- a/filer/87310116_davidsen.xlsx
+++ b/filer/87310116_davidsen.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/87310116_davidsen.xlsx
+++ b/filer/87310116_davidsen.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +644,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1498,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2976,35 +2976,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4358,19 +4358,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4476,19 +4476,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -4786,6 +4786,13 @@
       <c r="F99" s="13">
         <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4817,19 +4824,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4839,19 +4846,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>3340531</v>
+        <v>3828293</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>3828293</v>
+        <v>4152270</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>4152270</v>
+        <v>3181483</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>3181483</v>
+        <v>3026948</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>3026948</v>
+        <v>6182937</v>
       </c>
     </row>
     <row r="3">
@@ -4861,19 +4868,19 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>1735</v>
+        <v>2542</v>
       </c>
       <c r="C3" s="16" t="n">
-        <v>2542</v>
+        <v>3195</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>3195</v>
+        <v>2505</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>2505</v>
+        <v>1947</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>1947</v>
+        <v>5532</v>
       </c>
     </row>
     <row r="4">
@@ -4883,19 +4890,19 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>2528109</v>
+        <v>2870160</v>
       </c>
       <c r="C4" s="16" t="n">
-        <v>2870160</v>
+        <v>3236703</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3236703</v>
+        <v>-2459033</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-2459033</v>
+        <v>-2299760</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>-2299760</v>
+        <v>-4866979</v>
       </c>
     </row>
     <row r="5">
@@ -4905,19 +4912,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>244294</v>
+        <v>256630</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>256630</v>
+        <v>254677</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>254677</v>
+        <v>225820</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>225820</v>
+        <v>222634</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>222634</v>
+        <v>400052</v>
       </c>
     </row>
     <row r="6">
@@ -4927,19 +4934,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>569863</v>
+        <v>704045</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>704045</v>
+        <v>664085</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>664085</v>
+        <v>499135</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>499135</v>
+        <v>506501</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>506501</v>
+        <v>921438</v>
       </c>
     </row>
     <row r="7">
@@ -4949,19 +4956,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>448217</v>
+        <v>486070</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>486070</v>
+        <v>490091</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>490091</v>
+        <v>443347</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>443347</v>
+        <v>426963</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>426963</v>
+        <v>846290</v>
       </c>
     </row>
     <row r="8">
@@ -4978,19 +4985,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>17426</v>
+        <v>21476</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>21476</v>
+        <v>22173</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>22173</v>
+        <v>26614</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>26614</v>
+        <v>18627</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>18627</v>
+        <v>39844</v>
       </c>
     </row>
     <row r="10">
@@ -5012,19 +5019,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>104220</v>
+        <v>196499</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>196499</v>
+        <v>151821</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>151821</v>
+        <v>29174</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>29174</v>
+        <v>60911</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>60911</v>
+        <v>35304</v>
       </c>
     </row>
     <row r="12">
@@ -5034,19 +5041,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>258</v>
+        <v>118</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>207</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="13">
@@ -5056,19 +5063,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>4352</v>
+        <v>3929</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>3929</v>
+        <v>5401</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>5401</v>
+        <v>12654</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>12654</v>
+        <v>12069</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>12069</v>
+        <v>19480</v>
       </c>
     </row>
     <row r="14">
@@ -5078,19 +5085,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>6394</v>
+        <v>7549</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>7549</v>
+        <v>6350</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>6350</v>
+        <v>7352</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>7352</v>
+        <v>2636</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>2636</v>
+        <v>9830</v>
       </c>
     </row>
     <row r="15">
@@ -5100,14 +5107,12 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>-2000</v>
+        <v>-4000</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="D15" s="16" t="n">
         <v>-1000</v>
       </c>
+      <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
     </row>
@@ -5118,19 +5123,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>102436</v>
+        <v>192997</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>192997</v>
+        <v>151025</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>151025</v>
+        <v>34665</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>34665</v>
+        <v>70551</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>70551</v>
+        <v>47384</v>
       </c>
     </row>
     <row r="17">
@@ -5140,19 +5145,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>22834</v>
+        <v>42246</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>42246</v>
+        <v>33896</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>33896</v>
+        <v>9472</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>9472</v>
+        <v>15747</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>15747</v>
+        <v>11185</v>
       </c>
     </row>
     <row r="18">
@@ -5162,19 +5167,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>79602</v>
+        <v>150751</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>150751</v>
+        <v>117129</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>117129</v>
+        <v>25193</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>25193</v>
+        <v>54804</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>54804</v>
+        <v>36199</v>
       </c>
     </row>
     <row r="19">
@@ -5184,19 +5189,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>936</v>
+        <v>975</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>975</v>
+        <v>954</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>954</v>
+        <v>853</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>853</v>
+        <v>770</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>770</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="20">
@@ -5206,19 +5211,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>26900</v>
+        <v>22000</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>22000</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>22000</v>
+        <v>39000</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>39000</v>
+        <v>4000</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>4000</v>
+        <v>17000</v>
       </c>
     </row>
   </sheetData>
@@ -5250,19 +5255,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -5272,19 +5277,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>15371</v>
+        <v>16589</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>16589</v>
+        <v>17765</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>17765</v>
+        <v>6928</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>6928</v>
+        <v>3416</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>3416</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="3">
@@ -5318,19 +5323,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>15371</v>
+        <v>16589</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>16589</v>
+        <v>17765</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>17765</v>
+        <v>6928</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6928</v>
+        <v>3416</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>3416</v>
+        <v>5369</v>
       </c>
     </row>
     <row r="6">
@@ -5341,12 +5346,14 @@
       </c>
       <c r="B6" s="16" t="n"/>
       <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" s="16" t="n">
-        <v>0</v>
+        <v>38371</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>38371</v>
+        <v>275146</v>
       </c>
     </row>
     <row r="7">
@@ -5368,19 +5375,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>50789</v>
+        <v>56252</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>56252</v>
+        <v>58592</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>58592</v>
+        <v>47137</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>47137</v>
+        <v>36876</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>36876</v>
+        <v>65070</v>
       </c>
     </row>
     <row r="9">
@@ -5390,19 +5397,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>11417</v>
+        <v>11315</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>11315</v>
+        <v>10325</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>10325</v>
+        <v>9545</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>9545</v>
+        <v>5392</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>5392</v>
+        <v>4989</v>
       </c>
     </row>
     <row r="10">
@@ -5413,13 +5420,13 @@
       </c>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
+      <c r="D10" s="16" t="n">
+        <v>36225</v>
+      </c>
       <c r="E10" s="16" t="n">
-        <v>36225</v>
-      </c>
-      <c r="F10" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -5428,19 +5435,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>62206</v>
+        <v>67567</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>67567</v>
+        <v>68917</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>68917</v>
+        <v>92907</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>92907</v>
+        <v>80639</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>80639</v>
+        <v>345205</v>
       </c>
     </row>
     <row r="12">
@@ -5450,19 +5457,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>771</v>
+        <v>889</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>889</v>
+        <v>1042</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1042</v>
+        <v>1231</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>1231</v>
+        <v>1438</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>1438</v>
+        <v>48255</v>
       </c>
     </row>
     <row r="13">
@@ -5472,19 +5479,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>5403</v>
+        <v>5691</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>5691</v>
+        <v>8139</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>8139</v>
+        <v>2799</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>2799</v>
+        <v>2601</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>2601</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="14">
@@ -5494,19 +5501,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>6174</v>
+        <v>6580</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>6580</v>
+        <v>9181</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>9181</v>
+        <v>4030</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>4030</v>
+        <v>4039</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>4039</v>
+        <v>50943</v>
       </c>
     </row>
     <row r="15">
@@ -5516,19 +5523,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>83751</v>
+        <v>90736</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>90736</v>
+        <v>95863</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>95863</v>
+        <v>103865</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>103865</v>
+        <v>88094</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>88094</v>
+        <v>401517</v>
       </c>
     </row>
     <row r="16">
@@ -5562,19 +5569,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>380226</v>
+        <v>529009</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>529009</v>
+        <v>570022</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>570022</v>
+        <v>385055</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>385055</v>
+        <v>408960</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>408960</v>
+        <v>843055</v>
       </c>
     </row>
     <row r="19">
@@ -5584,19 +5591,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>380226</v>
+        <v>529009</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>529009</v>
+        <v>570022</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>570022</v>
+        <v>385055</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>385055</v>
+        <v>408960</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>408960</v>
+        <v>843055</v>
       </c>
     </row>
     <row r="20">
@@ -5606,19 +5613,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>298508</v>
+        <v>386191</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>386191</v>
+        <v>395642</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>395642</v>
+        <v>298997</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>298997</v>
+        <v>357867</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>357867</v>
+        <v>713964</v>
       </c>
     </row>
     <row r="21">
@@ -5628,19 +5635,19 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>52061</v>
+        <v>93494</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>93494</v>
+        <v>269437</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>269437</v>
+        <v>238033</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>238033</v>
+        <v>222808</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>222808</v>
+        <v>341837</v>
       </c>
     </row>
     <row r="22">
@@ -5650,19 +5657,19 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>1600</v>
+        <v>2879</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>2879</v>
+        <v>6969</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>6969</v>
+        <v>6419</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>6419</v>
+        <v>1931</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>1931</v>
+        <v>12632</v>
       </c>
     </row>
     <row r="23">
@@ -5672,19 +5679,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>9559</v>
+        <v>11022</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>11022</v>
+        <v>11447</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>11447</v>
+        <v>9656</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>9656</v>
+        <v>8447</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>8447</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="24">
@@ -5694,11 +5701,9 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>95</v>
-      </c>
-      <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="C24" s="16" t="n"/>
       <c r="D24" s="16" t="n"/>
       <c r="E24" s="16" t="n"/>
       <c r="F24" s="16" t="n"/>
@@ -5709,13 +5714,13 @@
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" s="16" t="n"/>
       <c r="C25" s="16" t="n"/>
       <c r="D25" s="16" t="n"/>
       <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="F25" s="16" t="n">
+        <v>8088</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
@@ -5736,19 +5741,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>361823</v>
+        <v>493586</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>493586</v>
+        <v>683495</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>683495</v>
+        <v>553105</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>553105</v>
+        <v>591053</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>591053</v>
+        <v>1085134</v>
       </c>
     </row>
     <row r="28">
@@ -5780,19 +5785,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>74129</v>
+        <v>111953</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>111953</v>
+        <v>5203</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>5203</v>
+        <v>122353</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>122353</v>
+        <v>50512</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>50512</v>
+        <v>11929</v>
       </c>
     </row>
     <row r="30">
@@ -5802,19 +5807,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>816327</v>
+        <v>1134697</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>1134697</v>
+        <v>1258869</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>1258869</v>
+        <v>1060662</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>1060662</v>
+        <v>1050674</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>1050674</v>
+        <v>1940267</v>
       </c>
     </row>
     <row r="31">
@@ -5824,19 +5829,19 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>900078</v>
+        <v>1225433</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>1225433</v>
+        <v>1354732</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>1354732</v>
+        <v>1164527</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>1164527</v>
+        <v>1138768</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>1138768</v>
+        <v>2341784</v>
       </c>
     </row>
     <row r="32">
@@ -5858,7 +5863,7 @@
         <v>11300</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>11300</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="33">
@@ -5868,19 +5873,19 @@
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>721</v>
+        <v>839</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>839</v>
+        <v>992</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>992</v>
+        <v>1181</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>1181</v>
+        <v>1388</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>1388</v>
+        <v>45696</v>
       </c>
     </row>
     <row r="34">
@@ -5889,18 +5894,20 @@
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
+      <c r="B34" s="16" t="n">
+        <v>12939</v>
+      </c>
       <c r="C34" s="16" t="n">
-        <v>12939</v>
+        <v>13855</v>
       </c>
       <c r="D34" s="16" t="n">
-        <v>13855</v>
+        <v>5403</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>5403</v>
+        <v>2664</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>2664</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="35">
@@ -5909,15 +5916,15 @@
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>-1210</v>
-      </c>
-      <c r="C35" s="16" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n">
+        <v>-81</v>
+      </c>
       <c r="D35" s="16" t="n">
-        <v>-81</v>
+        <v>-187</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>-187</v>
+        <v>0</v>
       </c>
       <c r="F35" s="16" t="n">
         <v>0</v>
@@ -5942,19 +5949,19 @@
         </is>
       </c>
       <c r="B37" s="16" t="n">
-        <v>176645</v>
+        <v>314339</v>
       </c>
       <c r="C37" s="16" t="n">
-        <v>314339</v>
+        <v>430399</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>430399</v>
+        <v>463855</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>463855</v>
+        <v>521197</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>521197</v>
+        <v>1144001</v>
       </c>
     </row>
     <row r="38">
@@ -5964,19 +5971,19 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>187456</v>
+        <v>339431</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>339431</v>
+        <v>456465</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>456465</v>
+        <v>481552</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>481552</v>
+        <v>536549</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>536549</v>
+        <v>1202553</v>
       </c>
     </row>
     <row r="39">
@@ -5986,19 +5993,19 @@
         </is>
       </c>
       <c r="B39" s="16" t="n">
-        <v>906</v>
+        <v>2096</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>2096</v>
+        <v>3095</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>3095</v>
+        <v>1522</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>1522</v>
+        <v>495</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>495</v>
+        <v>7777</v>
       </c>
     </row>
     <row r="40">
@@ -6008,19 +6015,19 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>906</v>
+        <v>2096</v>
       </c>
       <c r="C40" s="16" t="n">
-        <v>2096</v>
+        <v>3095</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>3095</v>
+        <v>1522</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>1522</v>
+        <v>495</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>495</v>
+        <v>7777</v>
       </c>
     </row>
     <row r="41">
@@ -6030,14 +6037,12 @@
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>190000</v>
+        <v>175000</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>175000</v>
-      </c>
-      <c r="D41" s="16" t="n">
         <v>150000</v>
       </c>
+      <c r="D41" s="16" t="n"/>
       <c r="E41" s="16" t="n"/>
       <c r="F41" s="16" t="n"/>
     </row>
@@ -6051,7 +6056,9 @@
       <c r="C42" s="16" t="n"/>
       <c r="D42" s="16" t="n"/>
       <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="F42" s="16" t="n">
+        <v>138388</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
@@ -6060,19 +6067,19 @@
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>31605</v>
+        <v>33527</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>33527</v>
+        <v>26742</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>26742</v>
+        <v>19876</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>19876</v>
+        <v>11835</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>11835</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="44">
@@ -6082,14 +6089,14 @@
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>31496</v>
-      </c>
-      <c r="C44" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="C44" s="16" t="n"/>
       <c r="D44" s="16" t="n"/>
       <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="F44" s="16" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -6098,19 +6105,19 @@
         </is>
       </c>
       <c r="B45" s="16" t="n">
-        <v>253101</v>
+        <v>208527</v>
       </c>
       <c r="C45" s="16" t="n">
-        <v>208527</v>
+        <v>176742</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>176742</v>
+        <v>19876</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>19876</v>
+        <v>11835</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>11835</v>
+        <v>151870</v>
       </c>
     </row>
     <row r="46">
@@ -6119,19 +6126,19 @@
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
+      <c r="B46" s="16" t="n">
+        <v>15000</v>
+      </c>
       <c r="C46" s="16" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>25000</v>
+        <v>150000</v>
       </c>
       <c r="E46" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F46" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F46" s="16" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
@@ -6139,9 +6146,7 @@
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
-        <v>5418</v>
-      </c>
+      <c r="B47" s="16" t="n"/>
       <c r="C47" s="16" t="n"/>
       <c r="D47" s="16" t="n"/>
       <c r="E47" s="16" t="n"/>
@@ -6154,19 +6159,19 @@
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="C48" s="16" t="n">
-        <v>13</v>
+        <v>19171</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>19171</v>
+        <v>98</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>131</v>
+        <v>8875</v>
       </c>
     </row>
     <row r="49">
@@ -6175,15 +6180,17 @@
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
+      <c r="B49" s="16" t="n">
+        <v>6704</v>
+      </c>
       <c r="C49" s="16" t="n">
-        <v>6704</v>
+        <v>6785</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>6785</v>
+        <v>6867</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>6867</v>
+        <v>7535</v>
       </c>
       <c r="F49" s="16" t="n">
         <v>7535</v>
@@ -6196,19 +6203,19 @@
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>358868</v>
+        <v>526299</v>
       </c>
       <c r="C50" s="16" t="n">
-        <v>526299</v>
+        <v>516945</v>
       </c>
       <c r="D50" s="16" t="n">
-        <v>516945</v>
+        <v>400680</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>400680</v>
+        <v>491184</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>491184</v>
+        <v>795956</v>
       </c>
     </row>
     <row r="51">
@@ -6218,19 +6225,19 @@
         </is>
       </c>
       <c r="B51" s="16" t="n">
-        <v>13883</v>
+        <v>20061</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>20061</v>
+        <v>14357</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>14357</v>
+        <v>15230</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>15230</v>
+        <v>4785</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>4785</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="52">
@@ -6240,20 +6247,18 @@
         </is>
       </c>
       <c r="B52" s="16" t="n">
-        <v>8381</v>
+        <v>6585</v>
       </c>
       <c r="C52" s="16" t="n">
-        <v>6585</v>
+        <v>5937</v>
       </c>
       <c r="D52" s="16" t="n">
-        <v>5937</v>
+        <v>184</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>184</v>
-      </c>
-      <c r="F52" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="F52" s="16" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
@@ -6262,15 +6267,17 @@
         </is>
       </c>
       <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
+      <c r="C53" s="16" t="n">
+        <v>708</v>
+      </c>
       <c r="D53" s="16" t="n">
-        <v>708</v>
+        <v>455</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>455</v>
+        <v>9614</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>9614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -6280,19 +6287,19 @@
         </is>
       </c>
       <c r="B54" s="16" t="n">
-        <v>7282</v>
+        <v>3907</v>
       </c>
       <c r="C54" s="16" t="n">
-        <v>3907</v>
+        <v>31383</v>
       </c>
       <c r="D54" s="16" t="n">
-        <v>31383</v>
+        <v>10527</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>10527</v>
+        <v>17591</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>17591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -6302,19 +6309,19 @@
         </is>
       </c>
       <c r="B55" s="16" t="n">
-        <v>55477</v>
+        <v>88572</v>
       </c>
       <c r="C55" s="16" t="n">
-        <v>88572</v>
+        <v>96889</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>96889</v>
+        <v>77133</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>77133</v>
+        <v>58001</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>58001</v>
+        <v>100217</v>
       </c>
     </row>
     <row r="56">
@@ -6324,19 +6331,19 @@
         </is>
       </c>
       <c r="B56" s="16" t="n">
-        <v>9194</v>
+        <v>8238</v>
       </c>
       <c r="C56" s="16" t="n">
-        <v>8238</v>
+        <v>1255</v>
       </c>
       <c r="D56" s="16" t="n">
-        <v>1255</v>
+        <v>403</v>
       </c>
       <c r="E56" s="16" t="n">
-        <v>403</v>
+        <v>1048</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>1048</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="57">
@@ -6346,19 +6353,19 @@
         </is>
       </c>
       <c r="B57" s="16" t="n">
-        <v>458615</v>
+        <v>675379</v>
       </c>
       <c r="C57" s="16" t="n">
-        <v>675379</v>
+        <v>718430</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>718430</v>
+        <v>661577</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>661577</v>
+        <v>589889</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>589889</v>
+        <v>979584</v>
       </c>
     </row>
     <row r="58">
@@ -6368,19 +6375,19 @@
         </is>
       </c>
       <c r="B58" s="16" t="n">
-        <v>711716</v>
+        <v>883906</v>
       </c>
       <c r="C58" s="16" t="n">
-        <v>883906</v>
+        <v>895172</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>895172</v>
+        <v>681453</v>
       </c>
       <c r="E58" s="16" t="n">
-        <v>681453</v>
+        <v>601724</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>601724</v>
+        <v>1131454</v>
       </c>
     </row>
     <row r="59">
@@ -6390,19 +6397,19 @@
         </is>
       </c>
       <c r="B59" s="16" t="n">
-        <v>900078</v>
+        <v>1225433</v>
       </c>
       <c r="C59" s="16" t="n">
-        <v>1225433</v>
+        <v>1354732</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>1354732</v>
+        <v>1164527</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>1164527</v>
+        <v>1138768</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>1138768</v>
+        <v>2341784</v>
       </c>
     </row>
   </sheetData>
@@ -6441,13 +6448,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7161,7 +7168,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7279,7 +7286,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7455,7 +7462,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
